--- a/output/pdf_financials_xlsx/ANOR.xlsx
+++ b/output/pdf_financials_xlsx/ANOR.xlsx
@@ -1341,43 +1341,43 @@
         <v>-2.272062</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.495292</v>
+        <v>-5.495292</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7.361381</v>
+        <v>-7.361381</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>6.467767</v>
+        <v>-6.467767</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.718786</v>
+        <v>-3.718786</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.037447</v>
+        <v>-2.037447</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-4.147451</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.645511</v>
+        <v>-5.645511</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>5.574864</v>
+        <v>-5.574864</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>6.566464</v>
+        <v>-6.566464</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>14.222477</v>
+        <v>-14.222477</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4.853759</v>
+        <v>-4.853759</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5.462392</v>
+        <v>-5.462392</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.500084</v>
+        <v>-0.500084</v>
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
@@ -1653,43 +1653,43 @@
         <v>-2.272062</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.495292</v>
+        <v>-5.495292</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7.361381</v>
+        <v>-7.361381</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.467767</v>
+        <v>-6.467767</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.718786</v>
+        <v>-3.718786</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.037447</v>
+        <v>-2.037447</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-4.147451</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.645511</v>
+        <v>-5.645511</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>5.574864</v>
+        <v>-5.574864</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>6.566464</v>
+        <v>-6.566464</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>14.222477</v>
+        <v>-14.222477</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>4.853759</v>
+        <v>-4.853759</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5.462392</v>
+        <v>-5.462392</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.500084</v>
+        <v>-0.500084</v>
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
@@ -1845,43 +1845,43 @@
         <v>-2.272062</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.495292</v>
+        <v>-5.495292</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7.361381</v>
+        <v>-7.361381</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6.467767</v>
+        <v>-6.467767</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.718786</v>
+        <v>-3.718786</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.037447</v>
+        <v>-2.037447</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-4.147451</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.645511</v>
+        <v>-5.645511</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5.574864</v>
+        <v>-5.574864</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>6.566464</v>
+        <v>-6.566464</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>14.222477</v>
+        <v>-14.222477</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.853759</v>
+        <v>-4.853759</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>5.462392</v>
+        <v>-5.462392</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.500084</v>
+        <v>-0.500084</v>
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45.44124</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-61.0588</v>
+        <v>61.0588</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2173,43 +2173,43 @@
         <v>-2.272062</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.495292</v>
+        <v>-5.495292</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7.361381</v>
+        <v>-7.361381</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6.467767</v>
+        <v>-6.467767</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.718786</v>
+        <v>-3.718786</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.037447</v>
+        <v>-2.037447</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-4.147451</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.645511</v>
+        <v>-5.645511</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5.574864</v>
+        <v>-5.574864</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>6.566464</v>
+        <v>-6.566464</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>14.222477</v>
+        <v>-14.222477</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>4.853759</v>
+        <v>-4.853759</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>5.462392</v>
+        <v>-5.462392</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.500084</v>
+        <v>-0.500084</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2301,43 +2301,43 @@
         <v>-2.272062</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.496999</v>
+        <v>-5.493585</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7.366926</v>
+        <v>-7.355836</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.483389</v>
+        <v>-6.452145</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.777314</v>
+        <v>-3.660258</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.11877</v>
+        <v>-1.956124</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.904005</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.354746</v>
+        <v>-4.936276</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>5.972257</v>
+        <v>-5.177471</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>6.573054</v>
+        <v>-6.559874</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>14.270626</v>
+        <v>-14.174328</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>4.897959</v>
+        <v>-4.809559</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>5.506425</v>
+        <v>-5.418359</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.507651</v>
+        <v>-0.492517</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2457,43 +2457,43 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
@@ -6043,10 +6043,10 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.001914</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.024686</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>0</v>
@@ -6101,34 +6101,34 @@
         <v>1.516747</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>3.098225</v>
+        <v>3.671792</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>3.634693</v>
+        <v>9.229903</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.410729</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>11.349778</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>12.898054</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>13.196043</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>13.314716</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>13.382558</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>13.4075</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>13.506737</v>
       </c>
     </row>
     <row r="93">
@@ -10037,7 +10037,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10840,7 +10844,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11517,7 +11525,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -18344,7 +18356,11 @@
           <t>Warrants reserve (note 11(e))</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -18439,7 +18455,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -38604,10 +38624,10 @@
         </is>
       </c>
       <c r="R306" s="5" t="n">
-        <v>5.462392</v>
+        <v>-5.462392</v>
       </c>
       <c r="S306" s="5" t="n">
-        <v>0.500084</v>
+        <v>-0.500084</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -40473,13 +40493,13 @@
         </is>
       </c>
       <c r="P325" s="5" t="n">
-        <v>14.112256</v>
+        <v>-14.112256</v>
       </c>
       <c r="Q325" s="5" t="n">
-        <v>4.853759</v>
+        <v>-4.853759</v>
       </c>
       <c r="R325" s="5" t="n">
-        <v>5.462392</v>
+        <v>-5.462392</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -42063,10 +42083,10 @@
         </is>
       </c>
       <c r="P341" s="5" t="n">
-        <v>14.222477</v>
+        <v>-14.222477</v>
       </c>
       <c r="Q341" s="5" t="n">
-        <v>4.874119</v>
+        <v>-4.874119</v>
       </c>
       <c r="R341" t="inlineStr">
         <is>
@@ -42652,16 +42672,16 @@
         </is>
       </c>
       <c r="M347" s="5" t="n">
-        <v>5.645511</v>
+        <v>-5.645511</v>
       </c>
       <c r="N347" s="5" t="n">
-        <v>5.574864</v>
+        <v>-5.574864</v>
       </c>
       <c r="O347" s="5" t="n">
-        <v>6.566464</v>
+        <v>-6.566464</v>
       </c>
       <c r="P347" s="5" t="n">
-        <v>14.222477</v>
+        <v>-14.222477</v>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
@@ -42856,10 +42876,10 @@
         </is>
       </c>
       <c r="O349" s="5" t="n">
-        <v>7.37744</v>
+        <v>-7.37744</v>
       </c>
       <c r="P349" s="5" t="n">
-        <v>14.112256</v>
+        <v>-14.112256</v>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
@@ -44026,13 +44046,13 @@
         </is>
       </c>
       <c r="M361" s="5" t="n">
-        <v>5.672111</v>
+        <v>-5.672111</v>
       </c>
       <c r="N361" s="5" t="n">
-        <v>4.846807</v>
+        <v>-4.846807</v>
       </c>
       <c r="O361" s="5" t="n">
-        <v>7.37744</v>
+        <v>-7.37744</v>
       </c>
       <c r="P361" t="inlineStr">
         <is>
@@ -47445,10 +47465,10 @@
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>2.037447</v>
+        <v>-2.037447</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>4.147451</v>
+        <v>-4.147451</v>
       </c>
       <c r="M396" t="inlineStr">
         <is>
@@ -47649,10 +47669,10 @@
         </is>
       </c>
       <c r="K398" s="5" t="n">
-        <v>2.037447</v>
+        <v>-2.037447</v>
       </c>
       <c r="L398" s="5" t="n">
-        <v>4.145537</v>
+        <v>-4.145537</v>
       </c>
       <c r="M398" t="inlineStr">
         <is>
@@ -48343,10 +48363,10 @@
         </is>
       </c>
       <c r="J405" s="5" t="n">
-        <v>3.718786</v>
+        <v>-3.718786</v>
       </c>
       <c r="K405" s="5" t="n">
-        <v>2.037447</v>
+        <v>-2.037447</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -49627,10 +49647,10 @@
         </is>
       </c>
       <c r="I418" s="5" t="n">
-        <v>6.467767</v>
+        <v>-6.467767</v>
       </c>
       <c r="J418" s="5" t="n">
-        <v>3.718786</v>
+        <v>-3.718786</v>
       </c>
       <c r="K418" t="inlineStr">
         <is>
@@ -50314,10 +50334,10 @@
         </is>
       </c>
       <c r="G425" s="5" t="n">
-        <v>5.495292</v>
+        <v>-5.495292</v>
       </c>
       <c r="H425" s="5" t="n">
-        <v>7.361381</v>
+        <v>-7.361381</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ANOR.xlsx
+++ b/output/pdf_financials_xlsx/ANOR.xlsx
@@ -984,16 +984,16 @@
         <v>0.243172</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.162792</v>
+        <v>15.710958</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.129454</v>
+        <v>2.086884</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.085289</v>
+        <v>1.020017</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.08537699999999999</v>
+        <v>0.582931</v>
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
@@ -1048,16 +1048,16 @@
         <v>-0.243172</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.162792</v>
+        <v>-15.710958</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.129454</v>
+        <v>-2.086884</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.085289</v>
+        <v>-1.020017</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.08537699999999999</v>
+        <v>-0.582931</v>
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
@@ -1082,34 +1082,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000122</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005735</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.183595</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.126435</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.05795</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012721</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022028</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011209</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017407</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.062856</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -2170,34 +2170,34 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.272062</v>
+        <v>-2.272184</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.495292</v>
+        <v>-5.489557</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.361381</v>
+        <v>-7.177786</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.467767</v>
+        <v>-6.341332</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.718786</v>
+        <v>-3.660836</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.037447</v>
+        <v>-2.024726</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.147451</v>
+        <v>-4.125423</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.645511</v>
+        <v>-5.634302</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.574864</v>
+        <v>-5.557457</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.566464</v>
+        <v>-6.503608</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-14.222477</v>
@@ -2298,34 +2298,34 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.272062</v>
+        <v>-2.272184</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.493585</v>
+        <v>-5.48785</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.355836</v>
+        <v>-7.172241</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.452145</v>
+        <v>-6.32571</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.660258</v>
+        <v>-3.602308</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.956124</v>
+        <v>-1.943403</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.904005</v>
+        <v>-3.881977</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.936276</v>
+        <v>-4.925067</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.177471</v>
+        <v>-5.160064</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.559874</v>
+        <v>-6.497018</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-14.174328</v>
@@ -2639,28 +2639,28 @@
         <v>6.382573</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.296303</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.469162</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.829044</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.121544</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.021018</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.100205</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.421955</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.525692</v>
       </c>
     </row>
     <row r="35">
@@ -2755,28 +2755,28 @@
         <v>6.382573</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.296303</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.469162</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.829044</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.121544</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.021018</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.100205</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>3.421955</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.525692</v>
       </c>
     </row>
     <row r="37">
@@ -3451,28 +3451,28 @@
         <v>6.103914</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>8.827798</v>
+        <v>6.531495</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.501501</v>
+        <v>0.032339</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.22254</v>
+        <v>3.393496</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.134579</v>
+        <v>0.013035</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.030065</v>
+        <v>0.009046999999999999</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.10243</v>
+        <v>0.002225</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>3.438081</v>
+        <v>0.016126</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.548963</v>
+        <v>0.023271</v>
       </c>
     </row>
     <row r="49">
@@ -8069,19 +8069,19 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.265373</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.255298</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.158432</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0522</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="Q124" s="1" t="inlineStr">
         <is>
@@ -8133,19 +8133,19 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.265373</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.255298</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.158432</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0522</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="Q125" s="1" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -24178,7 +24178,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -38155,7 +38159,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -43511,7 +43515,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -47338,7 +47342,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -50217,7 +50221,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">

--- a/output/pdf_financials_xlsx/ANOR.xlsx
+++ b/output/pdf_financials_xlsx/ANOR.xlsx
@@ -914,22 +914,22 @@
         <v>0.234016</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.272012</v>
+        <v>0.855762</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.121012</v>
+        <v>1.565372</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.083539</v>
+        <v>1.048196</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.063572</v>
+        <v>0.760575</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.03289</v>
+        <v>0.575429</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.045979</v>
+        <v>0.22325</v>
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
         <v>0.7666269999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.378256</v>
+        <v>0.962006</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.243172</v>
+        <v>1.687532</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>15.710958</v>
@@ -1042,10 +1042,10 @@
         <v>-0.7666269999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.378256</v>
+        <v>-0.962006</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.243172</v>
+        <v>-1.687532</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-15.710958</v>
@@ -37532,7 +37532,11 @@
           <t>Personnel costs (note 11)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -41428,7 +41432,11 @@
           <t>Personnel costs (note 16)</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -43612,7 +43620,11 @@
           <t>Personnel costs (note 15)</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
